--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.84718010749066</v>
+        <v>7.612666767467232</v>
       </c>
       <c r="D2" t="n">
-        <v>57.5979254355874</v>
+        <v>9.359662883282953</v>
       </c>
       <c r="E2" t="n">
-        <v>12.17727513309118</v>
+        <v>1.978807209127316</v>
       </c>
       <c r="F2" t="n">
-        <v>10.41782482766332</v>
+        <v>1.69289653449529</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.5329412286271</v>
+        <v>6.749102949651903</v>
       </c>
       <c r="D3" t="n">
-        <v>37.10795063055895</v>
+        <v>6.030041977465829</v>
       </c>
       <c r="E3" t="n">
-        <v>12.17727513309118</v>
+        <v>1.978807209127316</v>
       </c>
       <c r="F3" t="n">
-        <v>10.41782482766332</v>
+        <v>1.69289653449529</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.5582280863009</v>
+        <v>10.3282120640239</v>
       </c>
       <c r="D4" t="n">
-        <v>46.99808526275802</v>
+        <v>7.637188855198179</v>
       </c>
       <c r="E4" t="n">
-        <v>12.17727513309118</v>
+        <v>1.978807209127316</v>
       </c>
       <c r="F4" t="n">
-        <v>10.41782482766332</v>
+        <v>1.69289653449529</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>69.96956082554223</v>
+        <v>11.37005363415061</v>
       </c>
       <c r="D5" t="n">
-        <v>33.03134902430527</v>
+        <v>5.367594216449607</v>
       </c>
       <c r="E5" t="n">
-        <v>12.17727513309118</v>
+        <v>1.978807209127316</v>
       </c>
       <c r="F5" t="n">
-        <v>10.41782482766332</v>
+        <v>1.69289653449529</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>71.17646064565838</v>
+        <v>11.56617485491949</v>
       </c>
       <c r="D6" t="n">
-        <v>28.62762078914965</v>
+        <v>4.651988378236818</v>
       </c>
       <c r="E6" t="n">
-        <v>12.17727513309118</v>
+        <v>1.978807209127316</v>
       </c>
       <c r="F6" t="n">
-        <v>10.41782482766332</v>
+        <v>1.69289653449529</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
